--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/82.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/82.xlsx
@@ -426,13 +426,13 @@
         <v>-8.015578990351488</v>
       </c>
       <c r="E2">
-        <v>-9.394470845262012</v>
+        <v>-7.572638581132181</v>
       </c>
       <c r="F2">
-        <v>-6.681253763510311</v>
+        <v>-6.953730310047957</v>
       </c>
       <c r="G2">
-        <v>-10.49949564483308</v>
+        <v>-8.859769197049905</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.225068880356227</v>
       </c>
       <c r="E3">
-        <v>-10.0020879021892</v>
+        <v>-9.007829734487116</v>
       </c>
       <c r="F3">
-        <v>-6.812985718107905</v>
+        <v>-6.89142962605081</v>
       </c>
       <c r="G3">
-        <v>-9.788019681897232</v>
+        <v>-9.067863468557414</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.539615129140097</v>
       </c>
       <c r="E4">
-        <v>-10.48912981018815</v>
+        <v>-8.377067646906728</v>
       </c>
       <c r="F4">
-        <v>-7.075340857534446</v>
+        <v>-6.898160939565958</v>
       </c>
       <c r="G4">
-        <v>-10.00116584589767</v>
+        <v>-9.212815704994403</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.913407702741589</v>
       </c>
       <c r="E5">
-        <v>-12.75545896901487</v>
+        <v>-9.703838075570019</v>
       </c>
       <c r="F5">
-        <v>-6.582263444692068</v>
+        <v>-6.868608104103683</v>
       </c>
       <c r="G5">
-        <v>-10.17234091355122</v>
+        <v>-9.005767565877305</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.325870686172898</v>
       </c>
       <c r="E6">
-        <v>-12.31950277629645</v>
+        <v>-10.87704795063321</v>
       </c>
       <c r="F6">
-        <v>-6.74312576737651</v>
+        <v>-6.716228263623909</v>
       </c>
       <c r="G6">
-        <v>-10.34138067933195</v>
+        <v>-8.941480082050198</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.742828151083046</v>
       </c>
       <c r="E7">
-        <v>-13.98799638205255</v>
+        <v>-11.78593532634269</v>
       </c>
       <c r="F7">
-        <v>-6.412355764152758</v>
+        <v>-6.527237897410007</v>
       </c>
       <c r="G7">
-        <v>-9.352504174023951</v>
+        <v>-8.77117568787347</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.12682022366336</v>
       </c>
       <c r="E8">
-        <v>-13.30858489820776</v>
+        <v>-12.75221658162538</v>
       </c>
       <c r="F8">
-        <v>-6.109154242277874</v>
+        <v>-6.522812758744252</v>
       </c>
       <c r="G8">
-        <v>-9.700283604015468</v>
+        <v>-8.712545926372977</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.43959447163172</v>
       </c>
       <c r="E9">
-        <v>-14.75660068995242</v>
+        <v>-13.42080954106585</v>
       </c>
       <c r="F9">
-        <v>-6.510918645391155</v>
+        <v>-6.427297026997052</v>
       </c>
       <c r="G9">
-        <v>-11.04354407766583</v>
+        <v>-8.167861868796688</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.65429446090528</v>
       </c>
       <c r="E10">
-        <v>-16.58249499526713</v>
+        <v>-13.70384369501925</v>
       </c>
       <c r="F10">
-        <v>-6.371150698619003</v>
+        <v>-6.284896942802504</v>
       </c>
       <c r="G10">
-        <v>-9.674209747348167</v>
+        <v>-7.969937593185821</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.74756245399768</v>
       </c>
       <c r="E11">
-        <v>-16.57947450310402</v>
+        <v>-15.12398220077269</v>
       </c>
       <c r="F11">
-        <v>-6.001093714582678</v>
+        <v>-6.375296263286313</v>
       </c>
       <c r="G11">
-        <v>-9.074607049820909</v>
+        <v>-7.907676163228748</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.71513510105348</v>
       </c>
       <c r="E12">
-        <v>-16.26621278514941</v>
+        <v>-15.38287505979121</v>
       </c>
       <c r="F12">
-        <v>-5.992687442179069</v>
+        <v>-6.2867595269077</v>
       </c>
       <c r="G12">
-        <v>-9.183265775510868</v>
+        <v>-7.144085592413692</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.55891936774499</v>
       </c>
       <c r="E13">
-        <v>-17.20378804369748</v>
+        <v>-16.16775470327464</v>
       </c>
       <c r="F13">
-        <v>-5.909352853090036</v>
+        <v>-6.263003606530215</v>
       </c>
       <c r="G13">
-        <v>-9.594462015852663</v>
+        <v>-7.163511873638135</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.29462826112041</v>
       </c>
       <c r="E14">
-        <v>-18.16879226931001</v>
+        <v>-17.42520325182852</v>
       </c>
       <c r="F14">
-        <v>-5.338804864003043</v>
+        <v>-5.675445921194137</v>
       </c>
       <c r="G14">
-        <v>-8.975899824021999</v>
+        <v>-6.329694700298519</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.948594693043509</v>
       </c>
       <c r="E15">
-        <v>-19.5683579176466</v>
+        <v>-18.02016322390426</v>
       </c>
       <c r="F15">
-        <v>-5.593268561366814</v>
+        <v>-5.709152190814049</v>
       </c>
       <c r="G15">
-        <v>-8.202907303875413</v>
+        <v>-5.876947802893331</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.547809341663402</v>
       </c>
       <c r="E16">
-        <v>-19.90920257078193</v>
+        <v>-19.45499662781259</v>
       </c>
       <c r="F16">
-        <v>-4.976831503266937</v>
+        <v>-5.299340612566271</v>
       </c>
       <c r="G16">
-        <v>-7.327883770208489</v>
+        <v>-5.828991240211448</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.126125157637507</v>
       </c>
       <c r="E17">
-        <v>-20.31005403299289</v>
+        <v>-20.04488470899975</v>
       </c>
       <c r="F17">
-        <v>-5.286188623312024</v>
+        <v>-5.461927596183342</v>
       </c>
       <c r="G17">
-        <v>-7.301187530979806</v>
+        <v>-5.044428363405109</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.718466972309493</v>
       </c>
       <c r="E18">
-        <v>-21.93907745929814</v>
+        <v>-21.08775604517417</v>
       </c>
       <c r="F18">
-        <v>-4.696861545203566</v>
+        <v>-5.011580687446974</v>
       </c>
       <c r="G18">
-        <v>-7.116190935699793</v>
+        <v>-5.336719739612901</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.354391628733282</v>
       </c>
       <c r="E19">
-        <v>-22.11668873835298</v>
+        <v>-21.64585423882748</v>
       </c>
       <c r="F19">
-        <v>-4.811582975184672</v>
+        <v>-4.954931954239127</v>
       </c>
       <c r="G19">
-        <v>-6.693195911056034</v>
+        <v>-4.754984056361089</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.064600000125655</v>
       </c>
       <c r="E20">
-        <v>-23.7979979255508</v>
+        <v>-23.03172578176488</v>
       </c>
       <c r="F20">
-        <v>-4.303151772531406</v>
+        <v>-4.72308517207399</v>
       </c>
       <c r="G20">
-        <v>-6.309003790678074</v>
+        <v>-4.976932960950448</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.863300297513923</v>
       </c>
       <c r="E21">
-        <v>-24.08509864916309</v>
+        <v>-23.72574159428441</v>
       </c>
       <c r="F21">
-        <v>-3.684665333477003</v>
+        <v>-4.230445965587693</v>
       </c>
       <c r="G21">
-        <v>-6.310503467807364</v>
+        <v>-4.521262851834083</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.75917292929465</v>
       </c>
       <c r="E22">
-        <v>-24.75403124415413</v>
+        <v>-24.68658415228389</v>
       </c>
       <c r="F22">
-        <v>-3.550635487704043</v>
+        <v>-4.099228427147238</v>
       </c>
       <c r="G22">
-        <v>-7.552007703217148</v>
+        <v>-4.797597398542589</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.749223879688037</v>
       </c>
       <c r="E23">
-        <v>-25.35518616867237</v>
+        <v>-25.22421364342253</v>
       </c>
       <c r="F23">
-        <v>-3.725126110899342</v>
+        <v>-4.078749528215228</v>
       </c>
       <c r="G23">
-        <v>-6.308344992115759</v>
+        <v>-4.598080750527331</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.81288459426671</v>
       </c>
       <c r="E24">
-        <v>-26.22591662239322</v>
+        <v>-25.28762133647793</v>
       </c>
       <c r="F24">
-        <v>-3.595852750753256</v>
+        <v>-3.551323861015769</v>
       </c>
       <c r="G24">
-        <v>-6.598335539173758</v>
+        <v>-4.754947640360157</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.926331573994856</v>
       </c>
       <c r="E25">
-        <v>-25.88707355476928</v>
+        <v>-25.39409481734628</v>
       </c>
       <c r="F25">
-        <v>-3.379034210009708</v>
+        <v>-3.961540510923515</v>
       </c>
       <c r="G25">
-        <v>-6.692484143765091</v>
+        <v>-5.152752723995602</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.057938411295867</v>
       </c>
       <c r="E26">
-        <v>-26.54429098750249</v>
+        <v>-25.41068714611038</v>
       </c>
       <c r="F26">
-        <v>-2.759465094759846</v>
+        <v>-3.672679685525897</v>
       </c>
       <c r="G26">
-        <v>-6.649440430663487</v>
+        <v>-5.187523383794566</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.17413138499958</v>
       </c>
       <c r="E27">
-        <v>-26.96534850073567</v>
+        <v>-26.30093985127829</v>
       </c>
       <c r="F27">
-        <v>-3.229025157036746</v>
+        <v>-3.607792838497208</v>
       </c>
       <c r="G27">
-        <v>-8.127671845949935</v>
+        <v>-5.425220553514237</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.248798873551683</v>
       </c>
       <c r="E28">
-        <v>-26.08782533600332</v>
+        <v>-26.40645782413102</v>
       </c>
       <c r="F28">
-        <v>-3.176422998591574</v>
+        <v>-3.74982719848342</v>
       </c>
       <c r="G28">
-        <v>-7.900896165964321</v>
+        <v>-5.234175591533976</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.255258205874917</v>
       </c>
       <c r="E29">
-        <v>-26.70377931357863</v>
+        <v>-25.07110593722319</v>
       </c>
       <c r="F29">
-        <v>-3.21308653983948</v>
+        <v>-3.777348877074031</v>
       </c>
       <c r="G29">
-        <v>-7.748362780242401</v>
+        <v>-5.55225942803823</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.180809250252596</v>
       </c>
       <c r="E30">
-        <v>-26.23045415334891</v>
+        <v>-25.55899466986158</v>
       </c>
       <c r="F30">
-        <v>-3.506384101046493</v>
+        <v>-3.760469234507185</v>
       </c>
       <c r="G30">
-        <v>-7.101012084402234</v>
+        <v>-6.034440385833078</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.020680554099867</v>
       </c>
       <c r="E31">
-        <v>-25.28585976008895</v>
+        <v>-25.20109578361337</v>
       </c>
       <c r="F31">
-        <v>-3.303279182656291</v>
+        <v>-4.115227515164907</v>
       </c>
       <c r="G31">
-        <v>-7.578359645709747</v>
+        <v>-6.016454191918219</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.774920905264954</v>
       </c>
       <c r="E32">
-        <v>-24.96660687102219</v>
+        <v>-24.69911443986311</v>
       </c>
       <c r="F32">
-        <v>-3.2805570647975</v>
+        <v>-3.846112483547821</v>
       </c>
       <c r="G32">
-        <v>-7.274726340484412</v>
+        <v>-5.867171761915863</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.455884787123741</v>
       </c>
       <c r="E33">
-        <v>-24.63881327997697</v>
+        <v>-24.4564606886361</v>
       </c>
       <c r="F33">
-        <v>-3.440960471940791</v>
+        <v>-3.903751115802013</v>
       </c>
       <c r="G33">
-        <v>-7.400292022243428</v>
+        <v>-5.525540014990773</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.079279136988421</v>
       </c>
       <c r="E34">
-        <v>-23.02179030979205</v>
+        <v>-24.45459948581895</v>
       </c>
       <c r="F34">
-        <v>-3.468328902561884</v>
+        <v>-3.807782267085482</v>
       </c>
       <c r="G34">
-        <v>-7.144794049159096</v>
+        <v>-5.411114318971403</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.665276773533739</v>
       </c>
       <c r="E35">
-        <v>-24.10472052703832</v>
+        <v>-23.58596571556365</v>
       </c>
       <c r="F35">
-        <v>-3.713121410497971</v>
+        <v>-3.881175618973518</v>
       </c>
       <c r="G35">
-        <v>-7.660014251435871</v>
+        <v>-5.373840886744749</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.240013741428477</v>
       </c>
       <c r="E36">
-        <v>-23.74361548119268</v>
+        <v>-23.31232361670216</v>
       </c>
       <c r="F36">
-        <v>-3.283673382966832</v>
+        <v>-3.818401108821969</v>
       </c>
       <c r="G36">
-        <v>-6.825637595900117</v>
+        <v>-5.373705154377639</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.825092581809874</v>
       </c>
       <c r="E37">
-        <v>-24.49162428930567</v>
+        <v>-22.71922937591757</v>
       </c>
       <c r="F37">
-        <v>-3.564501529659504</v>
+        <v>-3.826461123651208</v>
       </c>
       <c r="G37">
-        <v>-6.620757864111241</v>
+        <v>-4.46586087223438</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.446034197506422</v>
       </c>
       <c r="E38">
-        <v>-22.43870399656441</v>
+        <v>-21.96757061775441</v>
       </c>
       <c r="F38">
-        <v>-3.285552120236381</v>
+        <v>-3.598433115212977</v>
       </c>
       <c r="G38">
-        <v>-6.292755633171331</v>
+        <v>-4.300254142177878</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.125867501831562</v>
       </c>
       <c r="E39">
-        <v>-22.04685966915471</v>
+        <v>-22.17665479116256</v>
       </c>
       <c r="F39">
-        <v>-3.311722731593026</v>
+        <v>-3.912887179887489</v>
       </c>
       <c r="G39">
-        <v>-6.318961911660201</v>
+        <v>-4.103812990968605</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.878653643934405</v>
       </c>
       <c r="E40">
-        <v>-22.92981700269626</v>
+        <v>-21.72070991417427</v>
       </c>
       <c r="F40">
-        <v>-3.750229785041181</v>
+        <v>-3.934691466663978</v>
       </c>
       <c r="G40">
-        <v>-5.98347122671046</v>
+        <v>-3.746989150563798</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.715314263098479</v>
       </c>
       <c r="E41">
-        <v>-22.07604568413414</v>
+        <v>-20.97367925644695</v>
       </c>
       <c r="F41">
-        <v>-3.61230578410766</v>
+        <v>-3.905574352455575</v>
       </c>
       <c r="G41">
-        <v>-5.393522079975717</v>
+        <v>-3.388228641018519</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.637134904480331</v>
       </c>
       <c r="E42">
-        <v>-20.19605875679781</v>
+        <v>-20.34337454474133</v>
       </c>
       <c r="F42">
-        <v>-3.463965063083936</v>
+        <v>-3.856073601566485</v>
       </c>
       <c r="G42">
-        <v>-5.740487115764572</v>
+        <v>-3.505392158198866</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.638164938899247</v>
       </c>
       <c r="E43">
-        <v>-20.2095173815486</v>
+        <v>-20.32494365553011</v>
       </c>
       <c r="F43">
-        <v>-3.825379275823152</v>
+        <v>-3.911571732451843</v>
       </c>
       <c r="G43">
-        <v>-6.168444648171698</v>
+        <v>-3.191592167622429</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.709700084422551</v>
       </c>
       <c r="E44">
-        <v>-20.03867164266122</v>
+        <v>-19.4878280643682</v>
       </c>
       <c r="F44">
-        <v>-3.157659648550763</v>
+        <v>-3.911653740824721</v>
       </c>
       <c r="G44">
-        <v>-5.184927916091778</v>
+        <v>-2.686767078338965</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.834006042235843</v>
       </c>
       <c r="E45">
-        <v>-19.31244479452514</v>
+        <v>-18.85736032759831</v>
       </c>
       <c r="F45">
-        <v>-4.064773313395195</v>
+        <v>-3.751266901029486</v>
       </c>
       <c r="G45">
-        <v>-5.37165592668883</v>
+        <v>-3.22192669639877</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.994212186263451</v>
       </c>
       <c r="E46">
-        <v>-19.32733441706236</v>
+        <v>-17.96090361303989</v>
       </c>
       <c r="F46">
-        <v>-3.79879530913251</v>
+        <v>-3.880418491167359</v>
       </c>
       <c r="G46">
-        <v>-6.068055665238838</v>
+        <v>-2.997630615022069</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.176106839256062</v>
       </c>
       <c r="E47">
-        <v>-17.65362853772342</v>
+        <v>-17.80165982456016</v>
       </c>
       <c r="F47">
-        <v>-4.109268240069167</v>
+        <v>-4.119674191383135</v>
       </c>
       <c r="G47">
-        <v>-5.660477851171466</v>
+        <v>-3.084045785233665</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.364084963167642</v>
       </c>
       <c r="E48">
-        <v>-17.07429180097414</v>
+        <v>-17.26725460691498</v>
       </c>
       <c r="F48">
-        <v>-3.81588038681525</v>
+        <v>-4.36355466680874</v>
       </c>
       <c r="G48">
-        <v>-5.627332669232283</v>
+        <v>-2.566018240339588</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.549480678400026</v>
       </c>
       <c r="E49">
-        <v>-16.99181923234645</v>
+        <v>-17.06021277528429</v>
       </c>
       <c r="F49">
-        <v>-4.019531199323898</v>
+        <v>-4.275331053308385</v>
       </c>
       <c r="G49">
-        <v>-4.458190338219889</v>
+        <v>-3.15229268152574</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.729805819979099</v>
       </c>
       <c r="E50">
-        <v>-16.2486740053177</v>
+        <v>-16.18548367901467</v>
       </c>
       <c r="F50">
-        <v>-4.186430663639942</v>
+        <v>-4.329280965517911</v>
       </c>
       <c r="G50">
-        <v>-5.01716933143475</v>
+        <v>-3.168269374298263</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.904623025620777</v>
       </c>
       <c r="E51">
-        <v>-16.60594796215286</v>
+        <v>-15.94429262489214</v>
       </c>
       <c r="F51">
-        <v>-4.355659497092658</v>
+        <v>-4.388164633978511</v>
       </c>
       <c r="G51">
-        <v>-5.630550519496454</v>
+        <v>-2.9742316791505</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.081915844291925</v>
       </c>
       <c r="E52">
-        <v>-15.36866923682915</v>
+        <v>-15.1987291927433</v>
       </c>
       <c r="F52">
-        <v>-4.495348748961544</v>
+        <v>-4.523922454153711</v>
       </c>
       <c r="G52">
-        <v>-6.011650590340736</v>
+        <v>-2.997779589571336</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.2698002224749</v>
       </c>
       <c r="E53">
-        <v>-15.11240289273508</v>
+        <v>-14.49598701081099</v>
       </c>
       <c r="F53">
-        <v>-4.151146354117697</v>
+        <v>-4.303219698658435</v>
       </c>
       <c r="G53">
-        <v>-5.868128509576712</v>
+        <v>-3.382680166694701</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.475488475109626</v>
       </c>
       <c r="E54">
-        <v>-15.1460675685081</v>
+        <v>-14.60494662390955</v>
       </c>
       <c r="F54">
-        <v>-4.229265542038704</v>
+        <v>-4.554017041897416</v>
       </c>
       <c r="G54">
-        <v>-5.245795606376818</v>
+        <v>-3.132618109385852</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.710227271344683</v>
       </c>
       <c r="E55">
-        <v>-14.50890674715487</v>
+        <v>-14.07774167993657</v>
       </c>
       <c r="F55">
-        <v>-4.625525029576681</v>
+        <v>-4.636041982122624</v>
       </c>
       <c r="G55">
-        <v>-6.022237714975325</v>
+        <v>-3.566620697947687</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.974799999643333</v>
       </c>
       <c r="E56">
-        <v>-14.34058789676378</v>
+        <v>-13.51204923537239</v>
       </c>
       <c r="F56">
-        <v>-4.372117500651479</v>
+        <v>-4.689071578147639</v>
       </c>
       <c r="G56">
-        <v>-5.982593932142553</v>
+        <v>-3.585994010443502</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.268418387066851</v>
       </c>
       <c r="E57">
-        <v>-13.81455129908477</v>
+        <v>-13.07438580795307</v>
       </c>
       <c r="F57">
-        <v>-4.588221160326411</v>
+        <v>-4.846674275102065</v>
       </c>
       <c r="G57">
-        <v>-5.135521334463695</v>
+        <v>-3.231768948287024</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.590691840219521</v>
       </c>
       <c r="E58">
-        <v>-13.941031578119</v>
+        <v>-12.34681853151072</v>
       </c>
       <c r="F58">
-        <v>-4.477182651818151</v>
+        <v>-5.054173682564119</v>
       </c>
       <c r="G58">
-        <v>-6.151110631728074</v>
+        <v>-3.208194553501874</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.934875256236309</v>
       </c>
       <c r="E59">
-        <v>-12.36505922481361</v>
+        <v>-11.85260352068361</v>
       </c>
       <c r="F59">
-        <v>-4.698391539796537</v>
+        <v>-4.693184422302539</v>
       </c>
       <c r="G59">
-        <v>-5.950607441142115</v>
+        <v>-3.446282367595179</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.30112590922672</v>
       </c>
       <c r="E60">
-        <v>-12.16518596753707</v>
+        <v>-11.95736523837706</v>
       </c>
       <c r="F60">
-        <v>-4.764726373045319</v>
+        <v>-4.960424030119688</v>
       </c>
       <c r="G60">
-        <v>-5.526003491366271</v>
+        <v>-3.275772719595016</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.686592034191845</v>
       </c>
       <c r="E61">
-        <v>-13.14383901380871</v>
+        <v>-11.5640763277589</v>
       </c>
       <c r="F61">
-        <v>-5.060114733576997</v>
+        <v>-4.770072656262986</v>
       </c>
       <c r="G61">
-        <v>-6.019751495275332</v>
+        <v>-3.469919662745575</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.086337692309931</v>
       </c>
       <c r="E62">
-        <v>-11.8145779244412</v>
+        <v>-11.71018754161639</v>
       </c>
       <c r="F62">
-        <v>-4.711946943975948</v>
+        <v>-5.081342476641137</v>
       </c>
       <c r="G62">
-        <v>-5.944694806808976</v>
+        <v>-3.791062443328116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.503005945431973</v>
       </c>
       <c r="E63">
-        <v>-11.52207020286375</v>
+        <v>-11.9439292559963</v>
       </c>
       <c r="F63">
-        <v>-4.937650553481924</v>
+        <v>-4.969169933158445</v>
       </c>
       <c r="G63">
-        <v>-6.611312877687701</v>
+        <v>-4.232480653897918</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.927713895947258</v>
       </c>
       <c r="E64">
-        <v>-12.64673030809071</v>
+        <v>-10.72043520555194</v>
       </c>
       <c r="F64">
-        <v>-4.915799049763476</v>
+        <v>-5.273901449626299</v>
       </c>
       <c r="G64">
-        <v>-7.025912358843867</v>
+        <v>-3.91736637674239</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.35215877017659</v>
       </c>
       <c r="E65">
-        <v>-10.35305822320567</v>
+        <v>-10.59643653027391</v>
       </c>
       <c r="F65">
-        <v>-5.024167730132512</v>
+        <v>-4.863220913972985</v>
       </c>
       <c r="G65">
-        <v>-6.46051090728282</v>
+        <v>-4.29620203443781</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.76693265612175</v>
       </c>
       <c r="E66">
-        <v>-11.56943351250998</v>
+        <v>-10.36705573636338</v>
       </c>
       <c r="F66">
-        <v>-5.000550147111296</v>
+        <v>-5.063922738527666</v>
       </c>
       <c r="G66">
-        <v>-7.04979132381863</v>
+        <v>-4.637270988621224</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.15597611127861</v>
       </c>
       <c r="E67">
-        <v>-11.3249095015178</v>
+        <v>-9.999275719830434</v>
       </c>
       <c r="F67">
-        <v>-4.998596028408092</v>
+        <v>-5.028559734102156</v>
       </c>
       <c r="G67">
-        <v>-6.237731055763104</v>
+        <v>-4.376688017588571</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.50903619036026</v>
       </c>
       <c r="E68">
-        <v>-11.3067820200651</v>
+        <v>-10.32590549305568</v>
       </c>
       <c r="F68">
-        <v>-4.8185743960643</v>
+        <v>-5.053568974360076</v>
       </c>
       <c r="G68">
-        <v>-6.190552471282951</v>
+        <v>-4.130433087649884</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.80942221014722</v>
       </c>
       <c r="E69">
-        <v>-10.71183563341137</v>
+        <v>-9.572308548017235</v>
       </c>
       <c r="F69">
-        <v>-5.471269923752115</v>
+        <v>-5.150766291934958</v>
       </c>
       <c r="G69">
-        <v>-7.091272459425698</v>
+        <v>-4.475587255028759</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.0417258092657</v>
       </c>
       <c r="E70">
-        <v>-11.28806583699139</v>
+        <v>-9.720158695893664</v>
       </c>
       <c r="F70">
-        <v>-5.029137106181906</v>
+        <v>-5.288192444059396</v>
       </c>
       <c r="G70">
-        <v>-7.450244843885491</v>
+        <v>-4.716349989917795</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.19823463594284</v>
       </c>
       <c r="E71">
-        <v>-11.4266326131521</v>
+        <v>-10.18574469404428</v>
       </c>
       <c r="F71">
-        <v>-5.462598573779609</v>
+        <v>-5.204709577205262</v>
       </c>
       <c r="G71">
-        <v>-7.083237765401887</v>
+        <v>-4.628256373117789</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.26699810398344</v>
       </c>
       <c r="E72">
-        <v>-12.33243609806236</v>
+        <v>-10.45087779024536</v>
       </c>
       <c r="F72">
-        <v>-5.288288534678121</v>
+        <v>-5.245600277309654</v>
       </c>
       <c r="G72">
-        <v>-6.014004388219158</v>
+        <v>-4.709119758460027</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.24650665670002</v>
       </c>
       <c r="E73">
-        <v>-11.67809424632403</v>
+        <v>-10.31878220344162</v>
       </c>
       <c r="F73">
-        <v>-5.27363223022039</v>
+        <v>-5.312022917503132</v>
       </c>
       <c r="G73">
-        <v>-6.549720177929561</v>
+        <v>-4.547386366684472</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.13673543103184</v>
       </c>
       <c r="E74">
-        <v>-11.79736066626404</v>
+        <v>-10.31271857674535</v>
       </c>
       <c r="F74">
-        <v>-5.595549056826722</v>
+        <v>-5.32173055509654</v>
       </c>
       <c r="G74">
-        <v>-6.1288240391577</v>
+        <v>-4.26477171508797</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.94209834243004</v>
       </c>
       <c r="E75">
-        <v>-11.23127877293521</v>
+        <v>-10.39816182432207</v>
       </c>
       <c r="F75">
-        <v>-5.286905161115445</v>
+        <v>-5.517018170306523</v>
       </c>
       <c r="G75">
-        <v>-6.361959277124256</v>
+        <v>-4.043074411959596</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.67554391191789</v>
       </c>
       <c r="E76">
-        <v>-12.5003654996888</v>
+        <v>-11.6161492503731</v>
       </c>
       <c r="F76">
-        <v>-5.597974516582119</v>
+        <v>-5.741967137108548</v>
       </c>
       <c r="G76">
-        <v>-6.126294782365697</v>
+        <v>-3.811680520946697</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.34642235251675</v>
       </c>
       <c r="E77">
-        <v>-12.18334514830782</v>
+        <v>-11.2560676396532</v>
       </c>
       <c r="F77">
-        <v>-5.655239555137649</v>
+        <v>-5.563748860600652</v>
       </c>
       <c r="G77">
-        <v>-6.331952492356302</v>
+        <v>-3.61984102803701</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.97218144540709</v>
       </c>
       <c r="E78">
-        <v>-12.65577367068403</v>
+        <v>-11.88891282527711</v>
       </c>
       <c r="F78">
-        <v>-5.603094655498823</v>
+        <v>-5.705608435064873</v>
       </c>
       <c r="G78">
-        <v>-6.312844023503628</v>
+        <v>-3.538646588140845</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.57467116907942</v>
       </c>
       <c r="E79">
-        <v>-13.46853512863269</v>
+        <v>-12.40615965490723</v>
       </c>
       <c r="F79">
-        <v>-5.738759698524909</v>
+        <v>-5.853177117669188</v>
       </c>
       <c r="G79">
-        <v>-5.833768357424616</v>
+        <v>-3.415378424986082</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.17098031834305</v>
       </c>
       <c r="E80">
-        <v>-15.61874062848072</v>
+        <v>-12.51458943654689</v>
       </c>
       <c r="F80">
-        <v>-5.913903903601017</v>
+        <v>-6.087268775495911</v>
       </c>
       <c r="G80">
-        <v>-4.597140555594179</v>
+        <v>-3.039207756449776</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.783985508933352</v>
       </c>
       <c r="E81">
-        <v>-14.70675577654999</v>
+        <v>-13.5664271512565</v>
       </c>
       <c r="F81">
-        <v>-5.757699490822517</v>
+        <v>-5.752463380469421</v>
       </c>
       <c r="G81">
-        <v>-5.369964237918262</v>
+        <v>-2.964667513087546</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.42776817501689</v>
       </c>
       <c r="E82">
-        <v>-15.44147804192447</v>
+        <v>-14.11137918486554</v>
       </c>
       <c r="F82">
-        <v>-5.73523002502158</v>
+        <v>-6.112977986209197</v>
       </c>
       <c r="G82">
-        <v>-5.506242845042361</v>
+        <v>-3.297916958707201</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.116812323246432</v>
       </c>
       <c r="E83">
-        <v>-16.77016854356701</v>
+        <v>-15.44247883468016</v>
       </c>
       <c r="F83">
-        <v>-6.222340707461593</v>
+        <v>-6.517434169197875</v>
       </c>
       <c r="G83">
-        <v>-5.431328510034193</v>
+        <v>-2.48978961875233</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.86449218475552</v>
       </c>
       <c r="E84">
-        <v>-16.80305432181072</v>
+        <v>-15.36352036188243</v>
       </c>
       <c r="F84">
-        <v>-5.891465915761386</v>
+        <v>-6.335923960631253</v>
       </c>
       <c r="G84">
-        <v>-5.165087816674926</v>
+        <v>-3.185298820552274</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.67190859091669</v>
       </c>
       <c r="E85">
-        <v>-17.53350170772195</v>
+        <v>-16.42675624566934</v>
       </c>
       <c r="F85">
-        <v>-6.280772087320265</v>
+        <v>-6.768738059103668</v>
       </c>
       <c r="G85">
-        <v>-4.736693292256616</v>
+        <v>-3.076428219947802</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.540830669621528</v>
       </c>
       <c r="E86">
-        <v>-19.60103538608595</v>
+        <v>-17.55525196838079</v>
       </c>
       <c r="F86">
-        <v>-6.535134723860895</v>
+        <v>-6.272652844221725</v>
       </c>
       <c r="G86">
-        <v>-4.928615548804784</v>
+        <v>-2.366567803235117</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.470187719919597</v>
       </c>
       <c r="E87">
-        <v>-20.74538982477227</v>
+        <v>-19.23454145617118</v>
       </c>
       <c r="F87">
-        <v>-6.477720993356562</v>
+        <v>-6.423327490402837</v>
       </c>
       <c r="G87">
-        <v>-4.460570620462624</v>
+        <v>-1.911202264308365</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.450503514908734</v>
       </c>
       <c r="E88">
-        <v>-21.52313712169362</v>
+        <v>-20.64063716402684</v>
       </c>
       <c r="F88">
-        <v>-6.45842500307575</v>
+        <v>-6.490678730454854</v>
       </c>
       <c r="G88">
-        <v>-5.06886018948493</v>
+        <v>-2.166395667203084</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.476549827493068</v>
       </c>
       <c r="E89">
-        <v>-22.38124218988109</v>
+        <v>-20.88648801790326</v>
       </c>
       <c r="F89">
-        <v>-6.713667365798154</v>
+        <v>-6.542106263922856</v>
       </c>
       <c r="G89">
-        <v>-4.874167006320391</v>
+        <v>-2.470717565900588</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.536203620201194</v>
       </c>
       <c r="E90">
-        <v>-24.72858574870503</v>
+        <v>-22.96619876287389</v>
       </c>
       <c r="F90">
-        <v>-6.57769541264933</v>
+        <v>-6.657553757932515</v>
       </c>
       <c r="G90">
-        <v>-5.649582845801724</v>
+        <v>-2.604463605687144</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.619725730458903</v>
       </c>
       <c r="E91">
-        <v>-25.27376420601446</v>
+        <v>-25.26777303490231</v>
       </c>
       <c r="F91">
-        <v>-6.496456178905679</v>
+        <v>-6.587008747359005</v>
       </c>
       <c r="G91">
-        <v>-4.251943351123294</v>
+        <v>-3.215027519494929</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.720211913629162</v>
       </c>
       <c r="E92">
-        <v>-28.45893432641952</v>
+        <v>-26.83511864522309</v>
       </c>
       <c r="F92">
-        <v>-6.627865898583584</v>
+        <v>-6.949423627920803</v>
       </c>
       <c r="G92">
-        <v>-5.863606304370068</v>
+        <v>-2.763767057036874</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.824562633102985</v>
       </c>
       <c r="E93">
-        <v>-30.39770084637541</v>
+        <v>-28.48602818640741</v>
       </c>
       <c r="F93">
-        <v>-6.551644086198689</v>
+        <v>-6.652013636742592</v>
       </c>
       <c r="G93">
-        <v>-5.424687555682415</v>
+        <v>-3.085151507443781</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.922890006423385</v>
       </c>
       <c r="E94">
-        <v>-32.18792889040571</v>
+        <v>-30.56485135047253</v>
       </c>
       <c r="F94">
-        <v>-6.918921897598621</v>
+        <v>-6.398395288313377</v>
       </c>
       <c r="G94">
-        <v>-5.342248350663484</v>
+        <v>-3.373976742471957</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.009300343808547</v>
       </c>
       <c r="E95">
-        <v>-34.45500977591771</v>
+        <v>-33.13487809014966</v>
       </c>
       <c r="F95">
-        <v>-6.50766813170257</v>
+        <v>-6.406204307819569</v>
       </c>
       <c r="G95">
-        <v>-7.161783768866635</v>
+        <v>-4.062060390627316</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.072009739004594</v>
       </c>
       <c r="E96">
-        <v>-36.78035174377538</v>
+        <v>-35.62174846162394</v>
       </c>
       <c r="F96">
-        <v>-6.503727173783751</v>
+        <v>-6.432992881258702</v>
       </c>
       <c r="G96">
-        <v>-6.574833976390472</v>
+        <v>-4.563670940192147</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.108720789687389</v>
       </c>
       <c r="E97">
-        <v>-37.69140146582353</v>
+        <v>-38.34463836990398</v>
       </c>
       <c r="F97">
-        <v>-6.556957234720245</v>
+        <v>-6.352688460129109</v>
       </c>
       <c r="G97">
-        <v>-7.038260693705348</v>
+        <v>-4.859852207408583</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.110994073425635</v>
       </c>
       <c r="E98">
-        <v>-40.80682402956245</v>
+        <v>-40.17146780510128</v>
       </c>
       <c r="F98">
-        <v>-6.889283326110156</v>
+        <v>-6.249573285828626</v>
       </c>
       <c r="G98">
-        <v>-7.364461987871896</v>
+        <v>-5.465930332010656</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.082945554096792</v>
       </c>
       <c r="E99">
-        <v>-43.73479494022786</v>
+        <v>-42.62880120486053</v>
       </c>
       <c r="F99">
-        <v>-7.024708970956834</v>
+        <v>-6.098050805610749</v>
       </c>
       <c r="G99">
-        <v>-7.046421188459652</v>
+        <v>-6.147104871625555</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.024287237622781</v>
       </c>
       <c r="E100">
-        <v>-44.52566801906045</v>
+        <v>-45.52400181336944</v>
       </c>
       <c r="F100">
-        <v>-6.858113517477617</v>
+        <v>-6.213015775608279</v>
       </c>
       <c r="G100">
-        <v>-8.058901883462656</v>
+        <v>-6.455127960235965</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.948217150441819</v>
       </c>
       <c r="E101">
-        <v>-47.94682824119023</v>
+        <v>-47.49117771501245</v>
       </c>
       <c r="F101">
-        <v>-6.90862446241442</v>
+        <v>-6.160987675773248</v>
       </c>
       <c r="G101">
-        <v>-8.604271223965574</v>
+        <v>-6.414947869025831</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.843283144132487</v>
       </c>
       <c r="E102">
-        <v>-50.63224502705681</v>
+        <v>-49.62737211628075</v>
       </c>
       <c r="F102">
-        <v>-6.711284981147703</v>
+        <v>-5.865974565675037</v>
       </c>
       <c r="G102">
-        <v>-9.08346275913846</v>
+        <v>-7.341172300003123</v>
       </c>
     </row>
   </sheetData>
